--- a/Test_Results/Excel/Summary_Report.xlsx
+++ b/Test_Results/Excel/Summary_Report.xlsx
@@ -459,7 +459,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>470</v>
+        <v>780</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>466</v>
+        <v>776</v>
       </c>
     </row>
     <row r="6">
@@ -540,7 +540,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>99.15%</t>
+          <t>99.49%</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>143.48 seconds</t>
+          <t>84.73 seconds</t>
         </is>
       </c>
     </row>
